--- a/ARM Functions/Ability Edits/Steelworker.xlsx
+++ b/ARM Functions/Ability Edits/Steelworker.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44620983-9DB1-409D-8E50-917810EE21C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B954FC-EE55-4212-8866-E156E70B00EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{9FC447D9-4EE0-4FAA-B875-57F901559E3A}"/>
   </bookViews>
   <sheets>
     <sheet name="Steelworker" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>3900A0E3</t>
   </si>
@@ -116,9 +116,6 @@
     <t>1080BDE8</t>
   </si>
   <si>
-    <t>mov r1, 0x3</t>
-  </si>
-  <si>
     <t>str r1, [r0]</t>
   </si>
   <si>
@@ -149,48 +146,21 @@
     <t>Main (unedited) 0x4A</t>
   </si>
   <si>
-    <t>000FE5B4</t>
-  </si>
-  <si>
     <t>000DAA7C</t>
   </si>
   <si>
     <t>Call Function</t>
   </si>
   <si>
-    <t>bl 0x000FEAD4</t>
-  </si>
-  <si>
     <t>Target Type is Steel</t>
   </si>
   <si>
-    <t>always-apply is NA</t>
-  </si>
-  <si>
-    <t>430100EB</t>
-  </si>
-  <si>
     <t>mov r0, 0x8</t>
   </si>
   <si>
-    <t>mov r3, 0xFF</t>
-  </si>
-  <si>
-    <t>push {lr}</t>
-  </si>
-  <si>
-    <t>04E02DE5</t>
-  </si>
-  <si>
     <t>0800A0E3</t>
   </si>
   <si>
-    <t>FF30A0E3</t>
-  </si>
-  <si>
-    <t>04F09DE4</t>
-  </si>
-  <si>
     <t>Add Defensive Steel 0x4E/0x4F</t>
   </si>
   <si>
@@ -210,13 +180,34 @@
   </si>
   <si>
     <t>b 0x00083108</t>
+  </si>
+  <si>
+    <t>b 0x000FEAD4</t>
+  </si>
+  <si>
+    <t>Set Defensive Steel 0x6D/0xA7/0x6A</t>
+  </si>
+  <si>
+    <t>b 0x00103164</t>
+  </si>
+  <si>
+    <t>mov r1, 0x6</t>
+  </si>
+  <si>
+    <t>000FE300</t>
+  </si>
+  <si>
+    <t>F20100EA</t>
+  </si>
+  <si>
+    <t>941300EA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,15 +219,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -259,12 +254,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,15 +595,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D955AB-897B-403C-8449-BE92F50FF23A}">
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
-    <col min="2" max="2" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" customWidth="1"/>
-    <col min="4" max="4" width="28.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="9.35546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.0703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -621,349 +619,341 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" t="str">
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="str">
         <f t="shared" ref="A4:A7" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000DAA80</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" t="str">
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000DAA84</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6" t="str">
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000DAA88</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" t="str">
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>000DAA8C</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" t="str">
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="str">
         <f t="shared" ref="A11:A24" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
         <v>000DE614</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" t="str">
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE618</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13" t="str">
+    <row r="13" spans="1:12">
+      <c r="A13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE61C</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A14" t="str">
+      <c r="C13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE620</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15" t="str">
+    <row r="15" spans="1:12">
+      <c r="A15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE624</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C15" s="2" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$24)</f>
         <v>bne 0x000DE648</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" t="str">
+    <row r="16" spans="1:12">
+      <c r="A16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE628</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A17" t="str">
+      <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE62C</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A18" t="str">
+      <c r="C17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE630</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A19" t="str">
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE634</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19" s="2" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$17)</f>
         <v>bne 0x000DE62C</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A20" t="str">
+      <c r="E19" s="4"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE638</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A21" t="str">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE63C</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A22" t="str">
+      <c r="C21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE640</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A23" t="str">
+      <c r="C22" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE644</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A24" t="str">
+      <c r="C23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>000DE648</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14">
       <c r="A26" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A28" t="str">
-        <f t="shared" ref="A28:A31" si="2">DEC2HEX(HEX2DEC(A27)+4,8)</f>
-        <v>000FE5B8</v>
-      </c>
-      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="2" t="str">
+        <f t="shared" ref="A28:A33" si="2">DEC2HEX(HEX2DEC(A27)+4,8)</f>
+        <v>000FE304</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A29" t="str">
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="2" t="str">
+        <f>DEC2HEX(HEX2DEC(A28)+4,8)</f>
+        <v>000FE308</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>000FE5BC</v>
-      </c>
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A30" t="str">
-        <f t="shared" si="2"/>
-        <v>000FE5C0</v>
-      </c>
-      <c r="B30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A31" t="str">
-        <f t="shared" si="2"/>
-        <v>000FE5C4</v>
-      </c>
-      <c r="B31" t="s">
+        <v>000FE30C</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C31" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(C27,"push","pop"),"lr","pc")</f>
-        <v>pop {pc}</v>
       </c>
     </row>
   </sheetData>

--- a/ARM Functions/Ability Edits/Steelworker.xlsx
+++ b/ARM Functions/Ability Edits/Steelworker.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B954FC-EE55-4212-8866-E156E70B00EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195F0944-B6DF-402B-A2F4-AD40C01FF7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{9FC447D9-4EE0-4FAA-B875-57F901559E3A}"/>
+    <workbookView xWindow="16449" yWindow="0" windowWidth="16465" windowHeight="17914" xr2:uid="{9FC447D9-4EE0-4FAA-B875-57F901559E3A}"/>
   </bookViews>
   <sheets>
     <sheet name="Steelworker" sheetId="1" r:id="rId1"/>
@@ -188,9 +188,6 @@
     <t>Set Defensive Steel 0x6D/0xA7/0x6A</t>
   </si>
   <si>
-    <t>b 0x00103164</t>
-  </si>
-  <si>
     <t>mov r1, 0x6</t>
   </si>
   <si>
@@ -200,7 +197,10 @@
     <t>F20100EA</t>
   </si>
   <si>
-    <t>941300EA</t>
+    <t>841500EA</t>
+  </si>
+  <si>
+    <t>b 0x00103924</t>
   </si>
 </sst>
 </file>
@@ -635,7 +635,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -900,7 +900,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>40</v>
@@ -914,11 +914,11 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="2" t="str">
-        <f t="shared" ref="A28:A33" si="2">DEC2HEX(HEX2DEC(A27)+4,8)</f>
+        <f t="shared" ref="A28:A32" si="2">DEC2HEX(HEX2DEC(A27)+4,8)</f>
         <v>000FE304</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>48</v>
@@ -950,10 +950,10 @@
         <v>000FE30C</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
